--- a/Data/Regression Evidence 2025/Workday_NewHire_Slovenia_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_Slovenia_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{CC840D11-CECC-4DE2-A475-86C2EFC2E162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{A92A0B85-DD8D-4D5F-96CC-4E67259C04F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -250,10 +250,10 @@
     <t>Slovenia</t>
   </si>
   <si>
-    <t>Lizeth</t>
-  </si>
-  <si>
-    <t>Renner</t>
+    <t>Santino</t>
+  </si>
+  <si>
+    <t>Jaskolski-Ondricka</t>
   </si>
   <si>
     <t xml:space="preserve">070-417-626 </t>
@@ -280,7 +280,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 87967676</t>
+    <t>Auto 91011208</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -364,10 +364,10 @@
     <t>795 Recruitment (Zosig Depazi (10280602))</t>
   </si>
   <si>
-    <t>Waino</t>
-  </si>
-  <si>
-    <t>Connelly-Cronin</t>
+    <t>Eloisa</t>
+  </si>
+  <si>
+    <t>Koch</t>
   </si>
   <si>
     <t>No</t>
@@ -1214,7 +1214,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="10">
-        <v>10700261</v>
+        <v>10700461</v>
       </c>
       <c r="C2" s="33" t="s">
         <v>117</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="K2" s="16">
         <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-7</f>
-        <v>45846</v>
+        <v>45867</v>
       </c>
       <c r="L2" s="12" t="s">
         <v>72</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="U2" s="21">
         <f t="shared" ref="U2:U3" ca="1" si="1">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="V2" s="15" t="s">
         <v>82</v>
@@ -1319,15 +1319,15 @@
       </c>
       <c r="AJ2" s="16">
         <f t="shared" ref="AJ2:AL3" ca="1" si="2">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AK2" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AL2" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AM2" s="21" t="str">
         <f t="shared" ref="AM2:AM3" si="3">AF2</f>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AU2" s="16">
         <f t="shared" ref="AU2:AU3" ca="1" si="4">TODAY()+7</f>
-        <v>45860</v>
+        <v>45881</v>
       </c>
       <c r="AV2" s="12" t="s">
         <v>72</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="AX2" s="29">
         <f t="array" aca="1" ref="AX2:AX3" ca="1">_xlfn.RANDARRAY(2,1,1023456789000,9999999999999,TRUE)</f>
-        <v>4508834923209</v>
+        <v>4859642532813</v>
       </c>
       <c r="AY2" s="16" t="s">
         <v>97</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="BC2" s="29">
         <f t="array" aca="1" ref="BC2:BC3" ca="1">_xlfn.RANDARRAY(2,1,12345678,99999999,TRUE)</f>
-        <v>40861965</v>
+        <v>57637609</v>
       </c>
       <c r="BD2" s="16" t="s">
         <v>97</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="BQ2" s="32">
         <f t="array" aca="1" ref="BQ2:BQ3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>97503</v>
+        <v>33569</v>
       </c>
       <c r="BR2" s="16">
         <v>44562</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="BU2" s="21">
         <f t="shared" ref="BU2:BU3" ca="1" si="5">TODAY()+365</f>
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="BV2" s="15" t="s">
         <v>108</v>
@@ -1449,7 +1449,7 @@
         <v>109</v>
       </c>
       <c r="B3" s="10">
-        <v>10700262</v>
+        <v>10700462</v>
       </c>
       <c r="C3" s="33" t="s">
         <v>117</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="K3" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>45846</v>
+        <v>45867</v>
       </c>
       <c r="L3" s="12" t="s">
         <v>72</v>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="U3" s="21">
         <f t="shared" ca="1" si="1"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="V3" s="15" t="s">
         <v>82</v>
@@ -1554,15 +1554,15 @@
       </c>
       <c r="AJ3" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AK3" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AL3" s="16">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AM3" s="21" t="str">
         <f t="shared" si="3"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="AU3" s="16">
         <f t="shared" ca="1" si="4"/>
-        <v>45860</v>
+        <v>45881</v>
       </c>
       <c r="AV3" s="12" t="s">
         <v>72</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AX3" s="29">
         <f ca="1"/>
-        <v>6021367736358</v>
+        <v>5082630747872</v>
       </c>
       <c r="AY3" s="16" t="s">
         <v>97</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="BC3" s="29">
         <f ca="1"/>
-        <v>54526600</v>
+        <v>14255899</v>
       </c>
       <c r="BD3" s="16" t="s">
         <v>97</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="BQ3" s="32">
         <f ca="1"/>
-        <v>58668</v>
+        <v>68169</v>
       </c>
       <c r="BR3" s="16">
         <v>44562</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="BU3" s="21">
         <f t="shared" ca="1" si="5"/>
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="BV3" s="15" t="s">
         <v>108</v>
